--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12790"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>##var</t>
   </si>
@@ -116,28 +116,10 @@
     <t>Entity.EntityId</t>
   </si>
   <si>
-    <t>Cat</t>
-  </si>
-  <si>
-    <t>猫猫</t>
-  </si>
-  <si>
-    <t>GanTan</t>
-  </si>
-  <si>
-    <t>感叹号</t>
-  </si>
-  <si>
-    <t>Anger</t>
-  </si>
-  <si>
-    <t>愤怒</t>
-  </si>
-  <si>
-    <t>LightningBall</t>
-  </si>
-  <si>
-    <t>闪电球</t>
+    <t>Wizard</t>
+  </si>
+  <si>
+    <t>角色</t>
   </si>
 </sst>
 </file>
@@ -145,10 +127,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -623,19 +605,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1100,7 +1082,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -1258,30 +1240,6 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
-      <c r="H10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="H11" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="H12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I12" t="s">
-        <v>36</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -3,8 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Godot-Project\StartFromZero\Configs\GameConfig\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -120,6 +125,12 @@
   </si>
   <si>
     <t>角色</t>
+  </si>
+  <si>
+    <t>Bug</t>
+  </si>
+  <si>
+    <t>蓝色虫子</t>
   </si>
 </sst>
 </file>
@@ -1082,7 +1093,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -1240,6 +1251,14 @@
         <v>30</v>
       </c>
     </row>
+    <row r="10" spans="1:12">
+      <c r="H10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
